--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:22</t>
+    <t xml:space="preserve">2026-09-10 01:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:36</t>
+    <t xml:space="preserve">2026-09-18 11:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:32</t>
+    <t xml:space="preserve">2026-09-23 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:37</t>
+    <t xml:space="preserve">2026-10-04 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2019_biobio.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:48</t>
+    <t xml:space="preserve">2026-10-05 16:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1058,7 +1058,7 @@
         <v>62.76</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>102.92</v>
+        <v>102.93</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>109.16</v>
